--- a/AtchisonRegime/Outputs/USA/USA500_Communication/df_regSummary_USA500_Communication.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Communication/df_regSummary_USA500_Communication.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.817335207728831</v>
+        <v>1.693190385616319</v>
       </c>
       <c r="H2" t="n">
-        <v>4.128712880280975</v>
+        <v>4.21215885625534</v>
       </c>
       <c r="I2" t="n">
         <v>-8.49080820295638</v>
@@ -545,22 +545,22 @@
         <v>8.955800344253511</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2569565713497336</v>
+        <v>0.2377582999627654</v>
       </c>
       <c r="O2" t="n">
         <v>-0.0260038557337664</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5988463879111421</v>
+        <v>0.5028550309763014</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>10.3135151779801</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>9.418745103146341</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>11.1380905480897</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
